--- a/data/trans_dic/P37A$medicoedad-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicoedad-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,03</t>
+          <t>6,14; 10,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 13,84</t>
+          <t>8,95; 13,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,97; 12,24</t>
+          <t>7,94; 12,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,37; 19,28</t>
+          <t>14,25; 19,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,77</t>
+          <t>8,01; 12,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,0; 13,93</t>
+          <t>9,1; 14,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,89</t>
+          <t>8,07; 12,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,78; 19,73</t>
+          <t>16,45; 20,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 10,64</t>
+          <t>7,68; 10,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 13,03</t>
+          <t>9,6; 12,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,95</t>
+          <t>8,72; 12,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,95; 18,77</t>
+          <t>15,9; 19,0</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,05</t>
+          <t>5,1; 8,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,66</t>
+          <t>7,89; 11,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 10,0</t>
+          <t>6,61; 10,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,92</t>
+          <t>8,75; 12,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,83; 11,65</t>
+          <t>7,75; 11,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 12,35</t>
+          <t>8,07; 12,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,12</t>
+          <t>8,97; 13,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,22; 17,64</t>
+          <t>13,89; 17,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 9,47</t>
+          <t>6,95; 9,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 11,42</t>
+          <t>8,51; 11,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,03</t>
+          <t>8,21; 10,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 13,47</t>
+          <t>11,93; 14,26</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,88</t>
+          <t>3,48; 6,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 9,91</t>
+          <t>5,58; 9,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,42</t>
+          <t>7,83; 12,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,79</t>
+          <t>9,36; 13,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 10,91</t>
+          <t>6,7; 11,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 11,56</t>
+          <t>7,17; 11,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,28</t>
+          <t>8,3; 13,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,78; 66,02</t>
+          <t>11,75; 15,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 8,28</t>
+          <t>5,56; 8,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 10,1</t>
+          <t>7,14; 10,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 12,19</t>
+          <t>8,64; 11,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,95; 48,16</t>
+          <t>11,25; 14,11</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,58</t>
+          <t>4,64; 7,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,4</t>
+          <t>6,83; 10,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 10,65</t>
+          <t>7,13; 10,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,32; 17,6</t>
+          <t>13,14; 17,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,24; 12,09</t>
+          <t>8,34; 12,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 12,97</t>
+          <t>9,12; 13,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,83; 13,22</t>
+          <t>8,89; 12,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,07; 18,2</t>
+          <t>15,35; 19,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 9,35</t>
+          <t>7,02; 9,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 11,07</t>
+          <t>8,45; 11,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 11,37</t>
+          <t>8,49; 11,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 17,18</t>
+          <t>14,72; 17,39</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 7,13</t>
+          <t>5,55; 7,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 10,19</t>
+          <t>8,09; 10,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 10,04</t>
+          <t>8,18; 10,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,52; 13,71</t>
+          <t>12,18; 14,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 10,77</t>
+          <t>8,7; 10,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,38; 11,44</t>
+          <t>9,4; 11,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,68; 11,97</t>
+          <t>9,63; 11,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,41; 34,86</t>
+          <t>15,25; 17,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 8,79</t>
+          <t>7,37; 8,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,07; 10,53</t>
+          <t>9,1; 10,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,22; 10,71</t>
+          <t>9,22; 10,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,62; 23,79</t>
+          <t>14,03; 15,4</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105499</t>
+          <t>113458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>125971</t>
+          <t>133794</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>231470</t>
+          <t>247252</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42913; 69640</t>
+          <t>42603; 70310</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62116; 97392</t>
+          <t>62960; 97866</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53783; 82572</t>
+          <t>53557; 84174</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>91291; 122543</t>
+          <t>98458; 132730</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>55361; 87932</t>
+          <t>55120; 86560</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62740; 97123</t>
+          <t>63430; 97883</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55064; 86711</t>
+          <t>54293; 87406</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>99926; 143091</t>
+          <t>120758; 148856</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>106871; 147087</t>
+          <t>106187; 149612</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133823; 182526</t>
+          <t>134433; 180775</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116300; 161064</t>
+          <t>117452; 161706</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>203418; 255445</t>
+          <t>226597; 270726</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97479</t>
+          <t>107429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>153104</t>
+          <t>168696</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>250583</t>
+          <t>276125</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47958; 77396</t>
+          <t>49064; 79119</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78748; 118660</t>
+          <t>80359; 120992</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66899; 102207</t>
+          <t>67633; 102674</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46242; 130295</t>
+          <t>91804; 126954</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75804; 112788</t>
+          <t>75065; 115012</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85454; 127483</t>
+          <t>83278; 124675</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92378; 136862</t>
+          <t>93595; 135923</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>136353; 169135</t>
+          <t>148800; 187695</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>135154; 182700</t>
+          <t>134235; 182628</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>176251; 234041</t>
+          <t>174385; 231476</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>170864; 227807</t>
+          <t>169481; 225968</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>163299; 289706</t>
+          <t>252918; 302434</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80042</t>
+          <t>92868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>303485</t>
+          <t>110825</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>383527</t>
+          <t>203692</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24265; 46710</t>
+          <t>23626; 46391</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43082; 75080</t>
+          <t>42238; 75404</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59898; 94308</t>
+          <t>59486; 94828</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64343; 97147</t>
+          <t>75187; 111255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45457; 74613</t>
+          <t>45805; 75573</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57082; 89844</t>
+          <t>55720; 90323</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66815; 104225</t>
+          <t>65189; 102692</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>119330; 616167</t>
+          <t>95460; 128056</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>75470; 112844</t>
+          <t>75782; 110907</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>107267; 154989</t>
+          <t>109561; 155549</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135508; 188279</t>
+          <t>133429; 183745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>195741; 788833</t>
+          <t>181796; 227904</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142129</t>
+          <t>149282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>175467</t>
+          <t>189700</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>317596</t>
+          <t>338983</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42980; 71418</t>
+          <t>43764; 72015</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63266; 98592</t>
+          <t>64717; 101486</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65960; 99890</t>
+          <t>66809; 99960</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123413; 163083</t>
+          <t>130055; 168586</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>85578; 125597</t>
+          <t>86615; 127063</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>95015; 136451</t>
+          <t>95920; 137523</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92178; 137997</t>
+          <t>92780; 135339</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>143114; 199308</t>
+          <t>171762; 213133</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>136029; 185214</t>
+          <t>139016; 186283</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>167731; 221268</t>
+          <t>168988; 223878</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>168499; 225364</t>
+          <t>168249; 222090</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>274595; 347308</t>
+          <t>310529; 366754</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>425149</t>
+          <t>463037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>758027</t>
+          <t>603015</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1183176</t>
+          <t>1066052</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>182065; 233678</t>
+          <t>181837; 233155</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>281299; 349296</t>
+          <t>277214; 352702</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>279868; 340765</t>
+          <t>277610; 344254</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>329445; 474346</t>
+          <t>430304; 497623</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>296561; 363853</t>
+          <t>294153; 367029</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>333750; 407204</t>
+          <t>334380; 408830</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>343255; 424348</t>
+          <t>341239; 423050</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>572244; 1294196</t>
+          <t>570051; 638987</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>494405; 585031</t>
+          <t>490841; 585437</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>633556; 735181</t>
+          <t>635343; 741090</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>639898; 743353</t>
+          <t>639817; 743952</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>976840; 1706409</t>
+          <t>1019898; 1119506</t>
         </is>
       </c>
     </row>
